--- a/client/public/import-templates/reisekosten-import-template-v1.xlsx
+++ b/client/public/import-templates/reisekosten-import-template-v1.xlsx
@@ -485,7 +485,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:AC1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,51 +525,60 @@
         <v>flight_route_type</v>
       </c>
       <c r="M1" t="str">
+        <v>departure_airport</v>
+      </c>
+      <c r="N1" t="str">
+        <v>arrival_airport</v>
+      </c>
+      <c r="O1" t="str">
+        <v>flight_direction</v>
+      </c>
+      <c r="P1" t="str">
         <v>departure_time</v>
       </c>
-      <c r="N1" t="str">
+      <c r="Q1" t="str">
         <v>arrival_time</v>
       </c>
-      <c r="O1" t="str">
+      <c r="R1" t="str">
         <v>return_date</v>
       </c>
-      <c r="P1" t="str">
+      <c r="S1" t="str">
         <v>ticket_number</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="T1" t="str">
         <v>flight_number</v>
       </c>
-      <c r="R1" t="str">
+      <c r="U1" t="str">
         <v>check_in_date</v>
       </c>
-      <c r="S1" t="str">
+      <c r="V1" t="str">
         <v>check_out_date</v>
       </c>
-      <c r="T1" t="str">
+      <c r="W1" t="str">
         <v>nights</v>
       </c>
-      <c r="U1" t="str">
+      <c r="X1" t="str">
         <v>distance_km</v>
       </c>
-      <c r="V1" t="str">
+      <c r="Y1" t="str">
         <v>rate_per_km</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <v>liters</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <v>price_per_liter</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AB1" t="str">
         <v>receipt_no</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AC1" t="str">
         <v>vendor_name</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC1"/>
   </ignoredErrors>
 </worksheet>
 </file>